--- a/calibration/phase2_bayesian_regression/renter_group/FI/FI_prob_metrics.xlsx
+++ b/calibration/phase2_bayesian_regression/renter_group/FI/FI_prob_metrics.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="36">
   <si>
     <t>N</t>
   </si>
@@ -112,34 +112,40 @@
     <t>none</t>
   </si>
   <si>
-    <t>platt</t>
-  </si>
-  <si>
-    <t>{'coef': 1.1879646824990364, 'intercept': -0.5905783650596893, 'C': 1.0}</t>
-  </si>
-  <si>
-    <t>{'coef': 0.8663609389266897, 'intercept': -0.3875920218968328, 'C': 1.0}</t>
-  </si>
-  <si>
-    <t>[0.40108473 0.54888323 0.53035526 0.19438943 0.57406901 0.13033906
- 0.37097222 0.35073649 0.3755868  0.5392108  0.46040541 0.30466382
- 0.14061197 0.67741124 0.46255153 0.32123906 0.53200749 0.50484885
- 0.48140799 0.56602038 0.28816769 0.40879237 0.28033356 0.45035003
- 0.36951553 0.39530371 0.57282891 0.45473836 0.58367567 0.60059272
- 0.29731218 0.33216189 0.50477373 0.38387487 0.35663992 0.17986932
- 0.10143525 0.26397952 0.70108643 0.34819606 0.31726735 0.27772598
- 0.59736733 0.3631835  0.3984221  0.41564075 0.09481787 0.19559201]</t>
-  </si>
-  <si>
-    <t>[0.4611275  0.3732712  0.2969084  0.33686435 0.5247629  0.37601027
- 0.23832372 0.46736994 0.40886262 0.4621127  0.5021617  0.25217992
- 0.19497293 0.3447527  0.32206345 0.3704661  0.33044517 0.3279813
- 0.34246495 0.5506123  0.53351945 0.16610688 0.3604695  0.39827818
- 0.3452101  0.2051191  0.2932615  0.18015194 0.18779097 0.49462706
- 0.16403903 0.34793842 0.33923358 0.5027501  0.3710475  0.5030766
- 0.41133854 0.5849704  0.44946402 0.3604696  0.21463783 0.34377387
- 0.50538    0.42962664 0.2813614  0.4924891  0.16531606 0.5876702
- 0.3697732  0.27319947]</t>
+    <t>temp</t>
+  </si>
+  <si>
+    <t>{'tau': 0.85}</t>
+  </si>
+  <si>
+    <t>[0.3724496  0.47125253 0.46836615 0.44234294 0.12263995 0.3444274
+ 0.5829678  0.24607286 0.5007316  0.79698056 0.7073561  0.60165477
+ 0.4167575  0.6893183  0.19852318 0.25636798 0.48753282 0.62373936
+ 0.15626413 0.25544852 0.58763164 0.37970966 0.68636227 0.30973148
+ 0.5517808  0.5937594  0.70981824 0.28075787 0.4562236  0.15529604
+ 0.43259475 0.36225408 0.6392748  0.5243542  0.4349313  0.507139
+ 0.20897776 0.36007956 0.35657713 0.46071047 0.26722673 0.59860986
+ 0.41569975 0.84791285 0.55074465 0.4857108  0.1573958  0.5354355
+ 0.14787461 0.5056571  0.49469286 0.6492878  0.5248365  0.55074465
+ 0.62815243 0.52755934 0.29681844 0.1695201  0.6836941  0.48871207
+ 0.4856116  0.28063172 0.27579826 0.5764046  0.3443477  0.53053397
+ 0.51092106 0.5011107  0.59778285 0.53412324 0.28496134 0.30069843
+ 0.5824998  0.399482   0.5135877 ]</t>
+  </si>
+  <si>
+    <t>[0.39744425 0.48946342 0.49432126 0.14800297 0.4792017  0.24964559
+ 0.5418633  0.5192461  0.7797964  0.30465347 0.255417   0.45620647
+ 0.27563596 0.21074982 0.1822585  0.22571628 0.27693492 0.73279595
+ 0.58895594 0.30497655 0.3663731  0.3860614  0.45707104 0.48533788
+ 0.47502807 0.23167334 0.49771848 0.45867652 0.35221106 0.55743957
+ 0.6562261  0.5824998  0.36620596 0.22835915 0.5335417  0.5852404
+ 0.4095666  0.36957636 0.5700689  0.26529267 0.6375242  0.41203284
+ 0.39344618 0.66354716 0.72628015 0.18120891 0.33903658 0.5465296
+ 0.42825484 0.65547    0.62552947 0.6224731  0.3960626  0.61164534
+ 0.17321044 0.4543857  0.5548971  0.85713065 0.5184542  0.39389592
+ 0.43365714 0.12077646 0.4053988  0.56165737 0.63303906 0.43805784
+ 0.5234035  0.33864057 0.72406346 0.66515225 0.16984585 0.3436575
+ 0.25578916 0.42240408 0.25558287 0.11824612 0.73612136]</t>
   </si>
 </sst>
 </file>
@@ -579,49 +585,49 @@
     </row>
     <row r="2" spans="1:25">
       <c r="A2">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="B2">
-        <v>0.3958333333333333</v>
+        <v>0.3066666666666666</v>
       </c>
       <c r="C2">
-        <v>0.222265288233757</v>
+        <v>0.2188096046447754</v>
       </c>
       <c r="D2">
-        <v>0.2391493055555556</v>
+        <v>0.2126222222222222</v>
       </c>
       <c r="E2">
-        <v>0.07060031925485277</v>
+        <v>-0.02910035629336249</v>
       </c>
       <c r="F2">
-        <v>0.6343382552875306</v>
+        <v>0.6277261034058557</v>
       </c>
       <c r="G2">
-        <v>0.1773733235895633</v>
+        <v>0.1778405231237412</v>
       </c>
       <c r="H2">
-        <v>0.2755082686742147</v>
+        <v>0.8116207122802734</v>
       </c>
       <c r="I2">
-        <v>0.04456353005982202</v>
+        <v>0.05556544672773676</v>
       </c>
       <c r="J2">
-        <v>0.05847719988344988</v>
+        <v>0.04597948010121923</v>
       </c>
       <c r="K2">
-        <v>0.2391493055555556</v>
+        <v>0.2126222222222222</v>
       </c>
       <c r="L2">
-        <v>0.7568058076225045</v>
+        <v>0.6964882943143813</v>
       </c>
       <c r="M2">
-        <v>0.7387522578872581</v>
+        <v>0.4333730818769181</v>
       </c>
       <c r="N2">
-        <v>0.2304622381925583</v>
+        <v>0.2275120317935944</v>
       </c>
       <c r="O2">
-        <v>0.1378456652164459</v>
+        <v>0.1441128849983215</v>
       </c>
       <c r="P2">
         <v>10</v>
@@ -644,49 +650,49 @@
     </row>
     <row r="3" spans="1:25">
       <c r="A3">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="B3">
-        <v>0.3958333333333333</v>
+        <v>0.3066666666666666</v>
       </c>
       <c r="C3">
-        <v>0.2008737663627283</v>
+        <v>0.2178677320480347</v>
       </c>
       <c r="D3">
-        <v>0.2391493055555556</v>
+        <v>0.2126222222222222</v>
       </c>
       <c r="E3">
-        <v>0.1600487156084828</v>
+        <v>-0.02467056251688549</v>
       </c>
       <c r="F3">
-        <v>0.5934325148310672</v>
+        <v>0.6257207177942258</v>
       </c>
       <c r="G3">
-        <v>0.1454116837647493</v>
+        <v>0.1467480713129044</v>
       </c>
       <c r="H3">
-        <v>0.3609980173363394</v>
+        <v>0.8479128479957581</v>
       </c>
       <c r="I3">
-        <v>0.02759738177116663</v>
+        <v>0.04132887559103083</v>
       </c>
       <c r="J3">
-        <v>0.0642936056998557</v>
+        <v>0.03457748917748917</v>
       </c>
       <c r="K3">
-        <v>0.2391493055555556</v>
+        <v>0.2126222222222222</v>
       </c>
       <c r="L3">
-        <v>0.7568058076225045</v>
+        <v>0.6964882943143813</v>
       </c>
       <c r="M3">
-        <v>0.7387522578872581</v>
+        <v>0.4333730818769181</v>
       </c>
       <c r="N3">
-        <v>0.2173017768159769</v>
+        <v>0.2208404242992401</v>
       </c>
       <c r="O3">
-        <v>0.1478155464488665</v>
+        <v>0.1642004102468491</v>
       </c>
       <c r="P3">
         <v>10</v>
@@ -710,54 +716,54 @@
         <v>33</v>
       </c>
       <c r="Y3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:25">
       <c r="A4">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="B4">
-        <v>0.36</v>
+        <v>0.3766233766233766</v>
       </c>
       <c r="C4">
-        <v>0.2160574197769165</v>
+        <v>0.2090375274419785</v>
       </c>
       <c r="D4">
-        <v>0.2304</v>
+        <v>0.2347782088041828</v>
       </c>
       <c r="E4">
-        <v>0.06225078221824432</v>
+        <v>0.1096382900836996</v>
       </c>
       <c r="F4">
-        <v>0.6241693094094154</v>
+        <v>0.6082948691283141</v>
       </c>
       <c r="G4">
-        <v>0.1455381333827972</v>
+        <v>0.1470172608440573</v>
       </c>
       <c r="H4">
-        <v>0.2980961799621582</v>
+        <v>0.2823934555053711</v>
       </c>
       <c r="I4">
-        <v>0.02821791806495353</v>
+        <v>0.02523466194299105</v>
       </c>
       <c r="J4">
-        <v>0.04198543417366947</v>
+        <v>0.05614082886810159</v>
       </c>
       <c r="K4">
-        <v>0.2304</v>
+        <v>0.2347782088041828</v>
       </c>
       <c r="L4">
-        <v>0.6822916666666666</v>
+        <v>0.7162356321839081</v>
       </c>
       <c r="M4">
-        <v>0.6683002737093038</v>
+        <v>0.6434946892394726</v>
       </c>
       <c r="N4">
-        <v>0.2276153117418289</v>
+        <v>0.22482830286026</v>
       </c>
       <c r="O4">
-        <v>0.1407260745763779</v>
+        <v>0.1504005938768387</v>
       </c>
       <c r="P4">
         <v>10</v>
@@ -780,49 +786,49 @@
     </row>
     <row r="5" spans="1:25">
       <c r="A5">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="B5">
-        <v>0.36</v>
+        <v>0.3766233766233766</v>
       </c>
       <c r="C5">
-        <v>0.2078319042921066</v>
+        <v>0.2069326490163803</v>
       </c>
       <c r="D5">
-        <v>0.2304</v>
+        <v>0.2347782088041828</v>
       </c>
       <c r="E5">
-        <v>0.09795180428773165</v>
+        <v>0.1186036810214665</v>
       </c>
       <c r="F5">
-        <v>0.6083457256215339</v>
+        <v>0.6039984593980894</v>
       </c>
       <c r="G5">
-        <v>0.1327848279476166</v>
+        <v>0.1482713327005312</v>
       </c>
       <c r="H5">
-        <v>0.2450107203589545</v>
+        <v>0.2762813462930567</v>
       </c>
       <c r="I5">
-        <v>0.0225373573329917</v>
+        <v>0.03023559894189322</v>
       </c>
       <c r="J5">
-        <v>0.04040000000000001</v>
+        <v>0.05537575063931061</v>
       </c>
       <c r="K5">
-        <v>0.2304</v>
+        <v>0.2347782088041828</v>
       </c>
       <c r="L5">
-        <v>0.6822916666666666</v>
+        <v>0.7162356321839081</v>
       </c>
       <c r="M5">
-        <v>0.6683002737093038</v>
+        <v>0.6434946892394726</v>
       </c>
       <c r="N5">
-        <v>0.2189666330814362</v>
+        <v>0.2173525542020798</v>
       </c>
       <c r="O5">
-        <v>0.1154211461544037</v>
+        <v>0.1713425815105438</v>
       </c>
       <c r="P5">
         <v>10</v>
@@ -843,10 +849,10 @@
         <v>32</v>
       </c>
       <c r="X5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Y5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
